--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.33203125" customWidth="1" style="8" min="4" max="5"/>
@@ -587,6 +587,10 @@
     <col width="21" customWidth="1" style="8" min="11" max="12"/>
     <col width="20.21875" customWidth="1" style="8" min="13" max="13"/>
     <col width="16.109375" customWidth="1" style="8" min="14" max="14"/>
+    <col width="20.21875" customWidth="1" style="8" min="28" max="28"/>
+    <col width="20.21875" customWidth="1" style="8" min="29" max="29"/>
+    <col width="20.21875" customWidth="1" style="8" min="30" max="30"/>
+    <col width="20.21875" customWidth="1" style="8" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2" customHeight="1" s="8">
@@ -673,6 +677,11 @@
       <c r="Y1" s="21" t="n"/>
       <c r="Z1" s="21" t="n"/>
       <c r="AA1" s="22" t="n"/>
+      <c r="AB1" s="11" t="inlineStr">
+        <is>
+          <t>RuntimeV1TargetPolicy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -758,6 +767,11 @@
       <c r="Y2" s="21" t="n"/>
       <c r="Z2" s="21" t="n"/>
       <c r="AA2" s="22" t="n"/>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>RuntimeV1TargetPolicy?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -818,6 +832,26 @@
       <c r="Y3" s="24" t="n"/>
       <c r="Z3" s="24" t="n"/>
       <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="26" t="inlineStr">
+        <is>
+          <t>Logical target</t>
+        </is>
+      </c>
+      <c r="AC3" s="26" t="inlineStr">
+        <is>
+          <t>Avatar binding</t>
+        </is>
+      </c>
+      <c r="AD3" s="26" t="inlineStr">
+        <is>
+          <t>Spatial binding</t>
+        </is>
+      </c>
+      <c r="AE3" s="26" t="inlineStr">
+        <is>
+          <t>Life policy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n"/>
@@ -852,6 +886,10 @@
           <t>1002;1001</t>
         </is>
       </c>
+      <c r="AB4" s="26" t="n"/>
+      <c r="AC4" s="26" t="n"/>
+      <c r="AD4" s="26" t="n"/>
+      <c r="AE4" s="26" t="n"/>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -877,6 +915,10 @@
           <t>1003</t>
         </is>
       </c>
+      <c r="AB5" s="26" t="n"/>
+      <c r="AC5" s="26" t="n"/>
+      <c r="AD5" s="26" t="n"/>
+      <c r="AE5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -902,6 +944,10 @@
           <t>1005</t>
         </is>
       </c>
+      <c r="AB6" s="26" t="n"/>
+      <c r="AC6" s="26" t="n"/>
+      <c r="AD6" s="26" t="n"/>
+      <c r="AE6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -935,6 +981,10 @@
       <c r="O7" t="n">
         <v>101</v>
       </c>
+      <c r="AB7" s="26" t="n"/>
+      <c r="AC7" s="26" t="n"/>
+      <c r="AD7" s="26" t="n"/>
+      <c r="AE7" s="26" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -986,6 +1036,10 @@
       <c r="O8" t="n">
         <v>103</v>
       </c>
+      <c r="AB8" s="26" t="n"/>
+      <c r="AC8" s="26" t="n"/>
+      <c r="AD8" s="26" t="n"/>
+      <c r="AE8" s="26" t="n"/>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1011,6 +1065,26 @@
           <t>9201</t>
         </is>
       </c>
+      <c r="AB9" s="26" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AC9" s="26" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AD9" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE9" s="26" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1036,6 +1110,26 @@
           <t>9202</t>
         </is>
       </c>
+      <c r="AB10" s="26" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AC10" s="26" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AD10" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE10" s="26" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -1059,6 +1153,26 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>9207</t>
+        </is>
+      </c>
+      <c r="AB11" s="26" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AC11" s="26" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AD11" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE11" s="26" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1222,34 @@
       <c r="Y12" s="26" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="26" t="n"/>
+      <c r="AB12" s="26" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AC12" s="26" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AD12" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE12" s="26" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N3:AA3"/>
+    <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="N2:AA2"/>
+    <mergeCell ref="AB1:AE1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
